--- a/sample/students_data.xlsx
+++ b/sample/students_data.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Smart Seating Allocator\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D73D789-284A-42B8-A4A9-E6B1FD6FC87D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Branch</t>
   </si>
@@ -22,65 +28,98 @@
     <t>No. of Students</t>
   </si>
   <si>
-    <t>CV5</t>
-  </si>
-  <si>
-    <t>ME5</t>
-  </si>
-  <si>
-    <t>CH5</t>
-  </si>
-  <si>
-    <t>CE5</t>
-  </si>
-  <si>
-    <t>IT5</t>
-  </si>
-  <si>
-    <t>CS5</t>
-  </si>
-  <si>
-    <t>IE5</t>
-  </si>
-  <si>
-    <t>ML5</t>
-  </si>
-  <si>
-    <t>CB5</t>
-  </si>
-  <si>
-    <t>CE/CSE5</t>
-  </si>
-  <si>
-    <t>BSCIT5</t>
-  </si>
-  <si>
-    <t>BCA5</t>
-  </si>
-  <si>
-    <t>DCV5</t>
-  </si>
-  <si>
-    <t>DME5</t>
-  </si>
-  <si>
-    <t>DCH5</t>
-  </si>
-  <si>
-    <t>DCE5</t>
-  </si>
-  <si>
-    <t>DIT5</t>
-  </si>
-  <si>
-    <t>DCEIT5</t>
+    <t>CV4</t>
+  </si>
+  <si>
+    <t>ME4</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>CE4</t>
+  </si>
+  <si>
+    <t>IT4</t>
+  </si>
+  <si>
+    <t>CSE4</t>
+  </si>
+  <si>
+    <t>ITE4</t>
+  </si>
+  <si>
+    <t>ML4</t>
+  </si>
+  <si>
+    <t>D2D4A</t>
+  </si>
+  <si>
+    <t>D2D4B</t>
+  </si>
+  <si>
+    <t>DS4</t>
+  </si>
+  <si>
+    <t>CB4</t>
+  </si>
+  <si>
+    <t>BSCIT4</t>
+  </si>
+  <si>
+    <t>BCA4</t>
+  </si>
+  <si>
+    <t>DCV4</t>
+  </si>
+  <si>
+    <t>DME4</t>
+  </si>
+  <si>
+    <t>DCH4</t>
+  </si>
+  <si>
+    <t>DCE4</t>
+  </si>
+  <si>
+    <t>DIT4</t>
+  </si>
+  <si>
+    <t>CV6</t>
+  </si>
+  <si>
+    <t>ME6</t>
+  </si>
+  <si>
+    <t>CH6</t>
+  </si>
+  <si>
+    <t>CE6</t>
+  </si>
+  <si>
+    <t>IT6</t>
+  </si>
+  <si>
+    <t>CSE6</t>
+  </si>
+  <si>
+    <t>ITE6</t>
+  </si>
+  <si>
+    <t>ML6</t>
+  </si>
+  <si>
+    <t>CB6</t>
+  </si>
+  <si>
+    <t>CE/CSE6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,16 +135,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -128,21 +189,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -189,7 +293,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -221,9 +325,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -255,6 +377,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -430,11 +570,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,148 +582,236 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
+      <c r="B17" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="B19" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="6">
         <v>15</v>
       </c>
-      <c r="B15">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="6">
         <v>18</v>
       </c>
-      <c r="B18">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
+    </row>
+    <row r="23" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="6">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="7">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="6">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="6">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="7">
         <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="5">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
